--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_sensitivity_p99_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep/param_sensitivity_p99_1Mbps.xlsx
@@ -64,7 +64,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,11 +94,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00161B22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="003D2B00"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -160,27 +155,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -615,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -674,7 +648,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All STAs</t>
+          <t>P-EDCA STAs</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -686,13 +660,13 @@
         <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>9580.4</v>
+        <v>10500.6</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>9603.5</v>
+        <v>15816.1</v>
       </c>
       <c r="F3" s="8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
@@ -703,7 +677,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>All STAs</t>
+          <t>P-EDCA STAs</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -715,13 +689,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>9412.5</v>
+        <v>8656.9</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>9975.799999999999</v>
+        <v>24893.1</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>0.046</v>
+        <v>-0.132</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -732,7 +706,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>All STAs</t>
+          <t>P-EDCA STAs</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -741,27 +715,27 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>9115.299999999999</v>
+        <v>8761.1</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>9966.5</v>
+        <v>20446.5</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>-0.285</v>
+        <v>0.145</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>mildly: smaller param → larger delay</t>
+          <t>no clear trend (≈flat)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>P-EDCA STAs</t>
+          <t>Legacy STAs</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -770,27 +744,27 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>8567.200000000001</v>
+        <v>11018.6</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>9827.6</v>
+        <v>11460</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.08799999999999999</v>
+        <v>-0.195</v>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>no clear trend (≈flat)</t>
+          <t>mildly: smaller param → larger delay</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>P-EDCA STAs</t>
+          <t>Legacy STAs</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -799,16 +773,16 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>8281.9</v>
+        <v>10305.4</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>12105.8</v>
+        <v>12102.9</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>-0.038</v>
+        <v>0.099</v>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
@@ -819,7 +793,7 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>P-EDCA STAs</t>
+          <t>Legacy STAs</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
@@ -828,47 +802,18 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>8312.799999999999</v>
+        <v>10999.6</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>9708.299999999999</v>
+        <v>11585.4</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.008</v>
+        <v>-0.048</v>
       </c>
       <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>no clear trend (≈flat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Legacy STAs</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>CWds</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>10323.6</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>10466.4</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>no clear trend (≈flat)</t>
         </is>
@@ -877,72 +822,14 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>Legacy STAs</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>QSRC</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>9997.9</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>10823.3</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>mildly: larger param → larger delay</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Legacy STAs</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>PSRC</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>10114.8</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>10718.3</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>no clear trend (≈flat)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
           <t>Notes: 'mean P99' is averaged over all other parameters and nPedca. Pearson corr is between the parameter level and P99 across every combo; positive = larger param worsens delay (so smaller is better), negative = larger is better. Legacy STAs only exist at nPedca=5/15 (none at 30).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A10:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -954,7 +841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -969,14 +856,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>All STAs — P99 VO delay sensitivity to CWds / QSRC / PSRC  (nSta=30, 1Mbps)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of CWds  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -1026,444 +913,111 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>9580.4</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>5632.5</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>12092.5</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>10008.3</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>9758.9</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>8973.9</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>▶ Effect of QSRC  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="n">
-        <v>9603.5</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>5552.5</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>11487.5</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>10016.9</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>9767.799999999999</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>9025.799999999999</v>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>54</v>
-      </c>
-      <c r="I6" s="33" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>QSRC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>mean P99 (all nPedca)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>min P99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>max P99</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>nPedca=5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>nPedca=15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>nPedca=30</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.009   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 9580 µs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>▶ Effect of QSRC  (mean P99 µs, averaged over the other 2 params)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>QSRC</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>▶ Effect of PSRC  (mean P99 µs, averaged over the other 2 params)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PSRC</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>mean P99 (all nPedca)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>min P99</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>max P99</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>nPedca=5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>nPedca=15</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>nPedca=30</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="B11" s="36" t="n">
-        <v>9764.200000000001</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>7422.5</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>11502.5</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>10233.3</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>9445</v>
-      </c>
-      <c r="G11" s="36" t="n">
-        <v>9614.200000000001</v>
-      </c>
-      <c r="H11" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="38" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="31" t="n">
-        <v>9442.200000000001</v>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>5552.5</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>11937.5</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>9916.700000000001</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>9506.700000000001</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>8903.299999999999</v>
-      </c>
-      <c r="H12" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I12" s="33" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>9412.5</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>7627.5</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>11487.5</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>10389.2</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>9190.799999999999</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>8657.5</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" s="29" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="31" t="n">
-        <v>9514.700000000001</v>
-      </c>
-      <c r="C14" s="31" t="n">
-        <v>8212.5</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>11407.5</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>9888.299999999999</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>10074.2</v>
-      </c>
-      <c r="G14" s="31" t="n">
-        <v>8581.700000000001</v>
-      </c>
-      <c r="H14" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I14" s="33" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="36" t="n">
-        <v>9442.200000000001</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>8257.5</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>12092.5</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>9398.299999999999</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>9725</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>9203.299999999999</v>
-      </c>
-      <c r="H15" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="I15" s="38" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="31" t="n">
-        <v>9975.799999999999</v>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>8337.5</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>11822.5</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>10250</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>10638.3</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <v>9039.200000000001</v>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I16" s="33" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.046   |   no clear trend (≈flat)   |   recommended QSRC = 2 (lowest mean P99 = 9412 µs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>▶ Effect of PSRC  (mean P99 µs, averaged over the other 2 params)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>PSRC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>mean P99 (all nPedca)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>min P99</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>max P99</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>nPedca=5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>nPedca=15</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>nPedca=30</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="36" t="n">
-        <v>9966.5</v>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>8257.5</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>11937.5</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>9762.5</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>9936.200000000001</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>10200.8</v>
-      </c>
-      <c r="H21" s="37" t="n">
-        <v>36</v>
-      </c>
-      <c r="I21" s="38" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="31" t="n">
-        <v>9694</v>
-      </c>
-      <c r="C22" s="31" t="n">
-        <v>7627.5</v>
-      </c>
-      <c r="D22" s="31" t="n">
-        <v>12092.5</v>
-      </c>
-      <c r="E22" s="31" t="n">
-        <v>10160.4</v>
-      </c>
-      <c r="F22" s="31" t="n">
-        <v>10047.9</v>
-      </c>
-      <c r="G22" s="31" t="n">
-        <v>8873.799999999999</v>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="I22" s="33" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="20" t="n">
-        <v>9115.299999999999</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>5552.5</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>11087.5</v>
-      </c>
-      <c r="E23" s="21" t="n">
-        <v>10115</v>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>9305.799999999999</v>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>7925</v>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="I23" s="29" t="inlineStr">
-        <is>
-          <t>◀ best (min P99)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.285   |   mildly: smaller param → larger delay   |   recommended PSRC = 3 (lowest mean P99 = 9115 µs)</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1490,14 +1044,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>P-EDCA STAs — P99 VO delay sensitivity to CWds / QSRC / PSRC  (nSta=30, 1Mbps)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of CWds  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -1547,72 +1101,72 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>8567.200000000001</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>4367.5</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>13157.5</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>8072.2</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>8523.1</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>9106.4</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>54</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="B5" s="13" t="n">
+        <v>10500.6</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>6032.5</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>75362.5</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>12077.2</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>9013.9</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>10410.8</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>108</v>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="31" t="n">
-        <v>9827.6</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>4872.5</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>81247.5</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>12046.4</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>8302.5</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <v>9133.9</v>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>54</v>
-      </c>
-      <c r="I6" s="33" t="inlineStr"/>
+      <c r="B6" s="24" t="n">
+        <v>15816.1</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>294222.5</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>28160.3</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>8574.4</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>10713.6</v>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>108</v>
+      </c>
+      <c r="I6" s="26" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.088   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 8567 µs)</t>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.093   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 10501 µs)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of QSRC  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -1662,180 +1216,180 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="36" t="n">
-        <v>8386.700000000001</v>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>4367.5</v>
-      </c>
-      <c r="D11" s="36" t="n">
-        <v>11072.5</v>
-      </c>
-      <c r="E11" s="36" t="n">
-        <v>7568.3</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>7654.2</v>
-      </c>
-      <c r="G11" s="36" t="n">
-        <v>9937.5</v>
-      </c>
-      <c r="H11" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="I11" s="38" t="inlineStr"/>
+      <c r="B11" s="29" t="n">
+        <v>16626.7</v>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>75362.5</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>30303.3</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>8688.299999999999</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>10888.3</v>
+      </c>
+      <c r="H11" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="I11" s="31" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="31" t="n">
-        <v>12105.8</v>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>5342.5</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>81247.5</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>19776.7</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>7458.3</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>9082.5</v>
-      </c>
-      <c r="H12" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I12" s="33" t="inlineStr"/>
+      <c r="B12" s="24" t="n">
+        <v>24893.1</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>294222.5</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>55985</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>8098.3</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>10595.8</v>
+      </c>
+      <c r="H12" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="I12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n">
+      <c r="A13" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>8281.9</v>
-      </c>
-      <c r="C13" s="21" t="n">
-        <v>7632.5</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>11017.5</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>7961.7</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>8174.2</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>8710</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" s="29" t="inlineStr">
+      <c r="B13" s="13" t="n">
+        <v>8656.9</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>7777.5</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>11127.5</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>8238.299999999999</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>8902.5</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>8830</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>36</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="31" t="n">
-        <v>8427.799999999999</v>
-      </c>
-      <c r="C14" s="31" t="n">
-        <v>8037.5</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>10187.5</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>8395</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>8295</v>
-      </c>
-      <c r="G14" s="31" t="n">
-        <v>8593.299999999999</v>
-      </c>
-      <c r="H14" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I14" s="33" t="inlineStr"/>
+      <c r="B14" s="24" t="n">
+        <v>8672.5</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>8202.5</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>10922.5</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>8456.700000000001</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>8725</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>8835.799999999999</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="I14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="36" t="n">
-        <v>8697.799999999999</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>8087.5</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>11262.5</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>8226.700000000001</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>8528.299999999999</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>9338.299999999999</v>
-      </c>
-      <c r="H15" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="I15" s="38" t="inlineStr"/>
+      <c r="B15" s="29" t="n">
+        <v>10005</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>8172.5</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>14552.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>8365.799999999999</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>9069.200000000001</v>
+      </c>
+      <c r="G15" s="29" t="n">
+        <v>12580</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>36</v>
+      </c>
+      <c r="I15" s="31" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="31" t="n">
-        <v>9284.4</v>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>8312.5</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>13157.5</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>8427.5</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>10366.7</v>
-      </c>
-      <c r="G16" s="31" t="n">
-        <v>9059.200000000001</v>
-      </c>
-      <c r="H16" s="32" t="n">
-        <v>18</v>
-      </c>
-      <c r="I16" s="33" t="inlineStr"/>
+      <c r="B16" s="24" t="n">
+        <v>10096.1</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>8567.5</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>15087.5</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>9363.299999999999</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>9281.700000000001</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>11643.3</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>36</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.038   |   no clear trend (≈flat)   |   recommended QSRC = 2 (lowest mean P99 = 8282 µs)</t>
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.132   |   no clear trend (≈flat)   |   recommended QSRC = 2 (lowest mean P99 = 8657 µs)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of PSRC  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -1885,94 +1439,94 @@
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n">
+      <c r="A21" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="36" t="n">
-        <v>9571.1</v>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>7697.5</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>12107.5</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>8954.200000000001</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>9487.5</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>10271.7</v>
-      </c>
-      <c r="H21" s="37" t="n">
-        <v>36</v>
-      </c>
-      <c r="I21" s="38" t="inlineStr"/>
+      <c r="B21" s="29" t="n">
+        <v>10267.5</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>8272.5</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>14382.5</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>9564.200000000001</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>10197.1</v>
+      </c>
+      <c r="G21" s="29" t="n">
+        <v>11041.2</v>
+      </c>
+      <c r="H21" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="I21" s="31" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n">
+      <c r="A22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>8312.799999999999</v>
-      </c>
-      <c r="C22" s="21" t="n">
-        <v>5752.5</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>13157.5</v>
-      </c>
-      <c r="E22" s="21" t="n">
-        <v>7657.9</v>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>8373.799999999999</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>8906.700000000001</v>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="I22" s="29" t="inlineStr">
+      <c r="B22" s="13" t="n">
+        <v>8761.1</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>6122.5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>14552.5</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>7642.1</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>8255.799999999999</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <v>10385.4</v>
+      </c>
+      <c r="H22" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n">
+      <c r="A23" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="36" t="n">
-        <v>9708.299999999999</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>4367.5</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>81247.5</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>13565.8</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>7377.1</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>8182.1</v>
-      </c>
-      <c r="H23" s="37" t="n">
-        <v>36</v>
-      </c>
-      <c r="I23" s="38" t="inlineStr"/>
+      <c r="B23" s="29" t="n">
+        <v>20446.5</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <v>5832.5</v>
+      </c>
+      <c r="D23" s="29" t="n">
+        <v>294222.5</v>
+      </c>
+      <c r="E23" s="29" t="n">
+        <v>43150</v>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>7929.6</v>
+      </c>
+      <c r="G23" s="29" t="n">
+        <v>10260</v>
+      </c>
+      <c r="H23" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="I23" s="31" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.008   |   no clear trend (≈flat)   |   recommended PSRC = 2 (lowest mean P99 = 8313 µs)</t>
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.145   |   no clear trend (≈flat)   |   recommended PSRC = 2 (lowest mean P99 = 8761 µs)</t>
         </is>
       </c>
     </row>
@@ -2011,14 +1565,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Legacy STAs — P99 VO delay sensitivity to CWds / QSRC / PSRC  (nSta=30, 1Mbps)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of CWds  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -2068,76 +1622,76 @@
       <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>10323.6</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>8267.5</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>12967.5</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>10332.2</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>10315</v>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="B5" s="29" t="n">
+        <v>11460</v>
+      </c>
+      <c r="C5" s="29" t="n">
+        <v>8357.5</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>13472.5</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>11408.9</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>11511.1</v>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="28" t="n">
-        <v>36</v>
-      </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="H5" s="30" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" s="31" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>11018.6</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>8357.5</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>13392.5</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>11029.4</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>11007.8</v>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>72</v>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="n">
-        <v>10466.4</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>8317.5</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>11972.5</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <v>10343.1</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <v>10589.7</v>
-      </c>
-      <c r="G6" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" s="32" t="n">
-        <v>36</v>
-      </c>
-      <c r="I6" s="33" t="inlineStr"/>
-    </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.069   |   no clear trend (≈flat)   |   recommended CWds = 0 (lowest mean P99 = 10324 µs)</t>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.195   |   mildly: smaller param → larger delay   |   recommended CWds = 1 (lowest mean P99 = 11019 µs)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of QSRC  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -2187,192 +1741,192 @@
       <c r="I10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="n">
+      <c r="A11" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>9997.9</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>8267.5</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>11807.5</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>10358.3</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>9637.5</v>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="B11" s="13" t="n">
+        <v>10305.4</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>8357.5</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>11957.5</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>9840.799999999999</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>10770</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="H11" s="21" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="31" t="n">
-        <v>10093.3</v>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>8332.5</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>11817.5</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>10155.8</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>10030.8</v>
-      </c>
-      <c r="G12" s="31" t="inlineStr">
+      <c r="B12" s="24" t="n">
+        <v>11392.5</v>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>8617.5</v>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>12567.5</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>11358.3</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>11426.7</v>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="I12" s="33" t="inlineStr"/>
+      <c r="H12" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I12" s="26" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="36" t="n">
-        <v>10581.2</v>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>8317.5</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>11972.5</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>10826.7</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>10335.8</v>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
+      <c r="B13" s="29" t="n">
+        <v>12102.9</v>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>10612.5</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>13472.5</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>12384.2</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>11821.7</v>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="I13" s="38" t="inlineStr"/>
+      <c r="H13" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" s="31" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="31" t="n">
-        <v>10823.3</v>
-      </c>
-      <c r="C14" s="31" t="n">
-        <v>8767.5</v>
-      </c>
-      <c r="D14" s="31" t="n">
-        <v>12677.5</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>10299.2</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>11347.5</v>
-      </c>
-      <c r="G14" s="31" t="inlineStr">
+      <c r="B14" s="24" t="n">
+        <v>11537.9</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>9837.5</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>13437.5</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>11155.8</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>11920</v>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="I14" s="33" t="inlineStr"/>
+      <c r="H14" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I14" s="26" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="36" t="n">
-        <v>10167.9</v>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>8432.5</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>12967.5</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>9839.200000000001</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>10496.7</v>
-      </c>
-      <c r="G15" s="36" t="inlineStr">
+      <c r="B15" s="29" t="n">
+        <v>10966.2</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>9267.5</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>12587.5</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>10835</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>11097.5</v>
+      </c>
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" s="38" t="inlineStr"/>
+      <c r="H15" s="30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I15" s="31" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="31" t="n">
-        <v>10706.2</v>
-      </c>
-      <c r="C16" s="31" t="n">
-        <v>9287.5</v>
-      </c>
-      <c r="D16" s="31" t="n">
-        <v>11767.5</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>10546.7</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>10865.8</v>
-      </c>
-      <c r="G16" s="31" t="inlineStr">
+      <c r="B16" s="24" t="n">
+        <v>11130.8</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>9917.5</v>
+      </c>
+      <c r="D16" s="24" t="n">
+        <v>13162.5</v>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>11740.8</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>10520.8</v>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="I16" s="33" t="inlineStr"/>
+      <c r="H16" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.190   |   mildly: larger param → larger delay   |   recommended QSRC = 0 (lowest mean P99 = 9998 µs)</t>
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.099   |   no clear trend (≈flat)   |   recommended QSRC = 0 (lowest mean P99 = 10305 µs)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>▶ Effect of PSRC  (mean P99 µs, averaged over the other 2 params)</t>
         </is>
@@ -2422,100 +1976,100 @@
       <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n">
+      <c r="A21" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>10114.8</v>
-      </c>
-      <c r="C21" s="21" t="n">
-        <v>8317.5</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>11767.5</v>
-      </c>
-      <c r="E21" s="21" t="n">
-        <v>9912.9</v>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>10316.7</v>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="B21" s="29" t="n">
+        <v>11132.9</v>
+      </c>
+      <c r="C21" s="29" t="n">
+        <v>8357.5</v>
+      </c>
+      <c r="D21" s="29" t="n">
+        <v>13437.5</v>
+      </c>
+      <c r="E21" s="29" t="n">
+        <v>11029.6</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>11236.2</v>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="28" t="n">
-        <v>24</v>
-      </c>
-      <c r="I21" s="29" t="inlineStr">
+      <c r="H21" s="30" t="n">
+        <v>48</v>
+      </c>
+      <c r="I21" s="31" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>11585.4</v>
+      </c>
+      <c r="C22" s="24" t="n">
+        <v>9617.5</v>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>13472.5</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>11669.2</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>11501.7</v>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="I22" s="26" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>10999.6</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>8617.5</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>12587.5</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>10958.8</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>11040.4</v>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>◀ best (min P99)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="31" t="n">
-        <v>10718.3</v>
-      </c>
-      <c r="C22" s="31" t="n">
-        <v>8332.5</v>
-      </c>
-      <c r="D22" s="31" t="n">
-        <v>12967.5</v>
-      </c>
-      <c r="E22" s="31" t="n">
-        <v>10523.8</v>
-      </c>
-      <c r="F22" s="31" t="n">
-        <v>10912.9</v>
-      </c>
-      <c r="G22" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="32" t="n">
-        <v>24</v>
-      </c>
-      <c r="I22" s="33" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="36" t="n">
-        <v>10351.9</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>8267.5</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>11837.5</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>10576.2</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>10127.5</v>
-      </c>
-      <c r="G23" s="36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="37" t="n">
-        <v>24</v>
-      </c>
-      <c r="I23" s="38" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   → Pearson corr(level, P99) = +0.094   |   no clear trend (≈flat)   |   recommended PSRC = 1 (lowest mean P99 = 10115 µs)</t>
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   → Pearson corr(level, P99) = -0.048   |   no clear trend (≈flat)   |   recommended PSRC = 3 (lowest mean P99 = 11000 µs)</t>
         </is>
       </c>
     </row>
